--- a/4_outputs/final/Table15.xlsx
+++ b/4_outputs/final/Table15.xlsx
@@ -417,142 +417,78 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Segments</t>
+          <t>LR CV acc.</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Research</t>
+          <t>kNN(5) CV acc.</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Policy</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Distinct docs</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Multi-parent units</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Mega-doc segments</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Mega-SDGs</t>
+          <t>Chance</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Original (per-SDG dedup)</t>
+          <t>Raw</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>0.691</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>0.554</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>204</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>390</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>15</t>
+          <t>0.059</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>One-per-parent (global dedup)</t>
+          <t>Adjusted (INLP)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>0.672</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>0.578</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>204</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>408</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>0.059</t>
         </is>
       </c>
     </row>
